--- a/AAII_Financials/Quarterly/NNGRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NNGRY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
   <si>
     <t>NNGRY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,56 +656,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -733,8 +739,14 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -762,8 +774,14 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -791,8 +809,14 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -804,8 +828,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -833,8 +859,14 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -862,8 +894,14 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -891,8 +929,14 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -920,8 +964,14 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -930,8 +980,10 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -959,8 +1011,14 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -988,8 +1046,14 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1001,8 +1065,10 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1030,8 +1096,14 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1059,8 +1131,14 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1088,8 +1166,14 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1117,8 +1201,14 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1146,8 +1236,14 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1175,8 +1271,14 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1204,8 +1306,14 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1233,8 +1341,14 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1262,8 +1376,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1291,8 +1411,14 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1320,8 +1446,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1349,8 +1481,14 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1378,8 +1516,14 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1407,8 +1551,14 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1436,8 +1586,14 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1465,42 +1621,54 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1512,8 +1680,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1525,95 +1695,115 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7173600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7728100</v>
+      </c>
+      <c r="F41" s="3">
         <v>7283800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>7334100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9071500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8686500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>7858100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>7820500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>7128400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>6540500</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>56908600</v>
+      </c>
+      <c r="E42" s="3">
+        <v>61307200</v>
+      </c>
+      <c r="F42" s="3">
         <v>56105200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>56492600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>54594900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>52277700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>49729300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>49491500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>46128000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>42324000</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1111900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1197900</v>
+      </c>
+      <c r="F43" s="3">
         <v>1128300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1136000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>921900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>882700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>976000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>971300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>733100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>672700</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1641,153 +1831,189 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5008800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5395900</v>
+      </c>
+      <c r="F45" s="3">
         <v>3728700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3754500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>5121000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>4903700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3909400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3890700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>4833800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>4435200</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>72878100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>78511000</v>
+      </c>
+      <c r="F46" s="3">
         <v>71698300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>72193300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>73025300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>69925900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>66890800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>66571100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>64168000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>58876300</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>78059800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>84093200</v>
+      </c>
+      <c r="F47" s="3">
         <v>77713500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>78250100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>84428000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>80844600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>83783800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>83383300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>86035100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>78940000</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>312700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>336800</v>
+      </c>
+      <c r="F48" s="3">
         <v>346100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>348500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>384700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>368300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>412700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>410700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>426400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>391300</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1272400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1370700</v>
+      </c>
+      <c r="F49" s="3">
         <v>1343600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1352900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1403800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1344200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1387600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1380900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1368000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1255100</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1815,8 +2041,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1844,37 +2076,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3144200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3387200</v>
+      </c>
+      <c r="F52" s="3">
         <v>3304400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3327200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3638800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>3484300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>3641900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3624500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3601600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3304600</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1902,37 +2146,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>217802000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>234636400</v>
+      </c>
+      <c r="F54" s="3">
         <v>219865000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>221383100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>230950600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>221148400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>223784900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>222715100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>221250400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>203004500</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1944,8 +2200,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1957,182 +2215,220 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>124900</v>
+      </c>
+      <c r="F57" s="3">
         <v>115700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>116500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>159200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>152400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>214000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>213000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>238300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>218700</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2897800</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>3121800</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>4650200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>4452800</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>6687000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>6135500</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2275600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2451500</v>
+      </c>
+      <c r="F59" s="3">
         <v>765000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>770300</v>
       </c>
-      <c r="F59" s="3">
-        <v>13988100</v>
-      </c>
-      <c r="G59" s="3">
-        <v>13394400</v>
-      </c>
       <c r="H59" s="3">
+        <v>2491400</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2385700</v>
+      </c>
+      <c r="J59" s="3">
         <v>780600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>776800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>12688900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>11642500</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5986100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6448800</v>
+      </c>
+      <c r="F60" s="3">
         <v>1585800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1596700</v>
       </c>
-      <c r="F60" s="3">
-        <v>19583300</v>
-      </c>
-      <c r="G60" s="3">
-        <v>18752100</v>
-      </c>
       <c r="H60" s="3">
+        <v>8086700</v>
+      </c>
+      <c r="I60" s="3">
+        <v>7743400</v>
+      </c>
+      <c r="J60" s="3">
         <v>1541500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1534100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>20064100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>18409500</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9275300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>9992200</v>
+      </c>
+      <c r="F61" s="3">
         <v>13086900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>13177300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>10935100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>10471000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>15306800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>15233600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>9772400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>8966500</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>179484400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>193357100</v>
+      </c>
+      <c r="F62" s="3">
         <v>181851500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>183107100</v>
       </c>
-      <c r="F62" s="3">
-        <v>176509300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>169017800</v>
-      </c>
       <c r="H62" s="3">
+        <v>188004900</v>
+      </c>
+      <c r="I62" s="3">
+        <v>180025400</v>
+      </c>
+      <c r="J62" s="3">
         <v>183498900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>182621700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>168109400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>154245900</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2160,8 +2456,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2189,8 +2491,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2218,37 +2526,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>195385700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>210487400</v>
+      </c>
+      <c r="F66" s="3">
         <v>197139200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>198500400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>207606900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>198795500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>201005500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>200044500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>198699400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>182313200</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2260,8 +2580,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2289,8 +2611,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2318,8 +2646,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2347,8 +2681,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2376,37 +2716,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="D72" s="3">
+        <v>-3039700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-3274600</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>-3335900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-3194300</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-3848500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-3531100</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2434,8 +2786,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2463,8 +2821,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2492,37 +2856,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22328400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>24054200</v>
+      </c>
+      <c r="F76" s="3">
         <v>22635800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>22792100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>23256300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>22269300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>22696500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>22588000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>22474100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>20620700</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2550,42 +2926,54 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2613,8 +3001,14 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2626,37 +3020,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F83" s="3">
         <v>40900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>40700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>38200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>40500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>14200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2684,8 +3086,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2713,8 +3121,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2742,8 +3156,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2771,8 +3191,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2800,37 +3226,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>111000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-321400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-323700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>125500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>120100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-90100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-89600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-612400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-561900</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2842,8 +3280,10 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2871,8 +3311,14 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2900,8 +3346,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2929,37 +3381,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>672400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>724400</v>
+      </c>
+      <c r="F94" s="3">
         <v>678200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>682900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>824000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>789100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>1660500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>1652500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>449400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>412300</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2971,37 +3435,45 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>214800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>231400</v>
+      </c>
+      <c r="F96" s="3">
         <v>187000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>188300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>115500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>110600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>157800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>157000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>110600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>101500</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3029,8 +3501,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3058,8 +3536,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3087,91 +3571,115 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-723700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-779600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1078400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1085900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-399000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-382100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1235800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1229900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>415700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>381400</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F101" s="3">
         <v>-46400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-46200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-19800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-18100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-54900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-58300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>4000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>73100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-754800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-760100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>557600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>534000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>288200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>286800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>233000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>213800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NNGRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NNGRY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
   <si>
     <t>NNGRY</t>
   </si>
@@ -656,62 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -745,8 +751,14 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -780,8 +792,14 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -815,8 +833,14 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -830,8 +854,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,8 +891,14 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -900,8 +932,14 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -935,8 +973,14 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -970,8 +1014,14 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -982,8 +1032,10 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1017,8 +1069,14 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1052,8 +1110,14 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1067,8 +1131,10 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1102,8 +1168,14 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1137,8 +1209,14 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1172,8 +1250,14 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1207,8 +1291,14 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1242,8 +1332,14 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1277,8 +1373,14 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1312,8 +1414,14 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1347,8 +1455,14 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1382,8 +1496,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1417,8 +1537,14 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1452,8 +1578,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1487,8 +1619,14 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1522,8 +1660,14 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1557,8 +1701,14 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1592,8 +1742,14 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1627,48 +1783,60 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1682,8 +1850,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1697,113 +1867,133 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9113300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8387400</v>
+      </c>
+      <c r="F41" s="3">
         <v>7173600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>7728100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>7283800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>7334100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>9071500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8686500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>7858100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>7820500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7128400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>6540500</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>63980000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>58883500</v>
+      </c>
+      <c r="F42" s="3">
         <v>56908600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>61307200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>56105200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>56492600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>54594900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>52277700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>49729300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>49491500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>46128000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>42324000</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1349400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1241900</v>
+      </c>
+      <c r="F43" s="3">
         <v>1111900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1197900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1128300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1136000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>921900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>882700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>976000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>971300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>733100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>672700</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1837,183 +2027,219 @@
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3439800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3165800</v>
+      </c>
+      <c r="F45" s="3">
         <v>5008800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>5395900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>3728700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>3754500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>5121000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>4903700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3909400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>3890700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>4833800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>4435200</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>81006500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>74553600</v>
+      </c>
+      <c r="F46" s="3">
         <v>72878100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>78511000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>71698300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>72193300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>73025300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>69925900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>66890800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>66571100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>64168000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>58876300</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>85894300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>79052100</v>
+      </c>
+      <c r="F47" s="3">
         <v>78059800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>84093200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>77713500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>78250100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>84428000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>80844600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>83783800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>83383300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>86035100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>78940000</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>323000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>297200</v>
+      </c>
+      <c r="F48" s="3">
         <v>312700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>336800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>346100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>348500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>384700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>368300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>412700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>410700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>426400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>391300</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1422200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1308900</v>
+      </c>
+      <c r="F49" s="3">
         <v>1272400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1370700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1343600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1352900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1403800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1344200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1387600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1380900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1368000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1255100</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2047,8 +2273,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2082,43 +2314,55 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3416300</v>
+      </c>
+      <c r="E52" s="3">
         <v>3144200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
+        <v>3144200</v>
+      </c>
+      <c r="G52" s="3">
         <v>3387200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3304400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>3327200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>3638800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3484300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3641900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3624500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3601600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3304600</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2152,43 +2396,55 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>242056400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>222774500</v>
+      </c>
+      <c r="F54" s="3">
         <v>217802000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>234636400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>219865000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>221383100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>230950600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>221148400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>223784900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>222715100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>221250400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>203004500</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2202,8 +2458,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2217,218 +2475,256 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>106900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>98400</v>
+      </c>
+      <c r="F57" s="3">
         <v>116000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>124900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>115700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>116500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>159200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>152400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>214000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>213000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>238300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>218700</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>2897800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3121800</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>4650200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>4452800</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>6687000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>6135500</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>441600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>406400</v>
+      </c>
+      <c r="F59" s="3">
         <v>2275600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2451500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>765000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>770300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2491400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2385700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>780600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>776800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>12688900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>11642500</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1153300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1061400</v>
+      </c>
+      <c r="F60" s="3">
         <v>5986100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6448800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1585800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1596700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>8086700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7743400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1541500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1534100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>20064100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>18409500</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15634800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>14389300</v>
+      </c>
+      <c r="F61" s="3">
         <v>9275300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>9992200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>13086900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>13177300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>10935100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>10471000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>15306800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>15233600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>9772400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>8966500</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>198716400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>182886900</v>
+      </c>
+      <c r="F62" s="3">
         <v>179484400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>193357100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>181851500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>183107100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>188004900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>180025400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>183498900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>182621700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>168109400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>154245900</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2462,8 +2758,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2497,8 +2799,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2532,43 +2840,55 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>216530800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>199282300</v>
+      </c>
+      <c r="F66" s="3">
         <v>195385700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>210487400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>197139200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>198500400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>207606900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>198795500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>201005500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>200044500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>198699400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>182313200</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2582,8 +2902,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2617,8 +2939,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2652,8 +2980,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2687,8 +3021,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2722,43 +3062,55 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
         <v>-3039700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-3274600</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>-3335900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-3194300</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>-3848500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-3531100</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2792,8 +3144,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2827,8 +3185,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2862,43 +3226,55 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25419800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>23394900</v>
+      </c>
+      <c r="F76" s="3">
         <v>22328400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>24054200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>22635800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>22792100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>23256300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>22269300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>22696500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>22588000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>22474100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>20620700</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2932,48 +3308,60 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3007,8 +3395,14 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3022,43 +3416,51 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>40500</v>
+      </c>
+      <c r="F83" s="3">
         <v>3900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>3700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>40900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>40700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>38200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>40500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>14200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3092,8 +3494,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3127,8 +3535,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3162,8 +3576,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3197,8 +3617,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3232,43 +3658,55 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>27000</v>
+      </c>
+      <c r="F89" s="3">
         <v>103000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>111000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-321400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-323700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>125500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>120100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-90100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-89600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-612400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-561900</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3282,8 +3720,10 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3317,8 +3757,14 @@
       <c r="M91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3352,8 +3798,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3387,43 +3839,55 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-115700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-106500</v>
+      </c>
+      <c r="F94" s="3">
         <v>672400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>724400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>678200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>682900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>824000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>789100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>1660500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>1652500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>449400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>412300</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3437,43 +3901,51 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>364100</v>
+      </c>
+      <c r="E96" s="3">
+        <v>335100</v>
+      </c>
+      <c r="F96" s="3">
         <v>214800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>231400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>187000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>188300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>115500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>110600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>157800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>157000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>110600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>101500</v>
       </c>
     </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3507,8 +3979,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3542,8 +4020,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3577,109 +4061,133 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>590100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>543100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-723700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-779600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1078400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1085900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-399000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-382100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1235800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1229900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>415700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>381400</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="F101" s="3">
         <v>7200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>6900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-46400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-46200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-19800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-18100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-54900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-58300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>488000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>449100</v>
+      </c>
+      <c r="F102" s="3">
         <v>67800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>73100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-754800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-760100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>557600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>534000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>288200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>286800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>233000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>213800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NNGRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NNGRY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="92">
   <si>
     <t>NNGRY</t>
   </si>
@@ -656,68 +656,74 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -757,8 +763,14 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -798,8 +810,14 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -839,8 +857,14 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -856,8 +880,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -897,8 +923,14 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -938,8 +970,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -979,8 +1017,14 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1020,8 +1064,14 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1034,8 +1084,10 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1075,8 +1127,14 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1116,8 +1174,14 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1133,8 +1197,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1174,8 +1240,14 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1215,8 +1287,14 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1256,8 +1334,14 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1297,8 +1381,14 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1338,8 +1428,14 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1379,8 +1475,14 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1420,8 +1522,14 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1461,8 +1569,14 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1502,8 +1616,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1543,8 +1663,14 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1584,8 +1710,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1625,8 +1757,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1666,8 +1804,14 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1707,8 +1851,14 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1748,8 +1898,14 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1789,54 +1945,66 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1852,8 +2020,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1869,131 +2039,151 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7519100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7513800</v>
+      </c>
+      <c r="F41" s="3">
         <v>9113300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>8387400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>7173600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>7728100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>7283800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>7334100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>9071500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>8686500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7858100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>7820500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>7128400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>6540500</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>66420100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>66373300</v>
+      </c>
+      <c r="F42" s="3">
         <v>63980000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>58883500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>56908600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>61307200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>56105200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>56492600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>54594900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>52277700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>49729300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>49491500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>46128000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>42324000</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>936900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>936300</v>
+      </c>
+      <c r="F43" s="3">
         <v>1349400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1241900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1111900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1197900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1128300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1136000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>921900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>882700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>976000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>971300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>733100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>672700</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2033,213 +2223,249 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3785400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3782700</v>
+      </c>
+      <c r="F45" s="3">
         <v>3439800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3165800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>5008800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>5395900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3728700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3754500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>5121000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>4903700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>3909400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>3890700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>4833800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>4435200</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>82659400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>82601200</v>
+      </c>
+      <c r="F46" s="3">
         <v>81006500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>74553600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>72878100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>78511000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>71698300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>72193300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>73025300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>69925900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>66890800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>66571100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>64168000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>58876300</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>84272600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>84213300</v>
+      </c>
+      <c r="F47" s="3">
         <v>85894300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>79052100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>78059800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>84093200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>77713500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>78250100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>84428000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>80844600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>83783800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>83383300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>86035100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>78940000</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>367500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>367200</v>
+      </c>
+      <c r="F48" s="3">
         <v>323000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>297200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>312700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>336800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>346100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>348500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>384700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>368300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>412700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>410700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>426400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>391300</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1396000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1395000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1422200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1308900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1272400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1370700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1343600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1352900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1403800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1344200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1387600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1380900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1368000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1255100</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2279,8 +2505,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2320,49 +2552,61 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3394400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3392000</v>
+      </c>
+      <c r="F52" s="3">
         <v>3416300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3144200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3144200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>3387200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>3304400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3327200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3638800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3484300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3641900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3624500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>3601600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>3304600</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2402,49 +2646,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>240591800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>240422400</v>
+      </c>
+      <c r="F54" s="3">
         <v>242056400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>222774500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>217802000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>234636400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>219865000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>221383100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>230950600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>221148400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>223784900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>222715100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>221250400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>203004500</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2460,8 +2716,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2477,254 +2735,292 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>81000</v>
+      </c>
+      <c r="F57" s="3">
         <v>106900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>98400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>116000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>124900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>115700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>116500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>159200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>152400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>214000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>213000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>238300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>218700</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>5552400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>5548500</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>2897800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3121800</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>4650200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>4452800</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>6687000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>6135500</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>763200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>762600</v>
+      </c>
+      <c r="F59" s="3">
         <v>441600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>406400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2275600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2451500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>765000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>770300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2491400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2385700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>780600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>776800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>12688900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>11642500</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7031800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7026900</v>
+      </c>
+      <c r="F60" s="3">
         <v>1153300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1061400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5986100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6448800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1585800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1596700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>8086700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7743400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1541500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1534100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>20064100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>18409500</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10520100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>10512700</v>
+      </c>
+      <c r="F61" s="3">
         <v>15634800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>14389300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>9275300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>9992200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>13086900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>13177300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>10935100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>10471000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>15306800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>15233600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>9772400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>8966500</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>197525000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>197385900</v>
+      </c>
+      <c r="F62" s="3">
         <v>198716400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>182886900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>179484400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>193357100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>181851500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>183107100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>188004900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>180025400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>183498900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>182621700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>168109400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>154245900</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2764,8 +3060,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2805,8 +3107,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2846,49 +3154,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>215753200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>215601300</v>
+      </c>
+      <c r="F66" s="3">
         <v>216530800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>199282300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>195385700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>210487400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>197139200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>198500400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>207606900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>198795500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>201005500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>200044500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>198699400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>182313200</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2904,8 +3224,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2945,8 +3267,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2986,8 +3314,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3027,8 +3361,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3068,49 +3408,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="D72" s="3">
+        <v>-3551700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-3549200</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>-3039700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-3274600</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-3335900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-3194300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>-3848500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-3531100</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3150,8 +3502,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3191,8 +3549,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3232,49 +3596,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24729400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>24712000</v>
+      </c>
+      <c r="F76" s="3">
         <v>25419800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>23394900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>22328400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>24054200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>22635800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>22792100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>23256300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>22269300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>22696500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>22588000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>22474100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>20620700</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3314,54 +3690,66 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3401,8 +3789,14 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3418,49 +3812,57 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F83" s="3">
         <v>40200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>40500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>3900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>3700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>40900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>40700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>38200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>40500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>14200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3500,8 +3902,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3541,8 +3949,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3582,8 +3996,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3623,8 +4043,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3664,49 +4090,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1406600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1405600</v>
+      </c>
+      <c r="F89" s="3">
         <v>29400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>27000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>103000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>111000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-321400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-323700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>125500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>120100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-90100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-89600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-612400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-561900</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3722,8 +4160,10 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3763,8 +4203,14 @@
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3804,8 +4250,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3845,49 +4297,61 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>761400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>760900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-115700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-106500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>672400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>724400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>678200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>682900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>824000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>789100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>1660500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>1652500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>449400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>412300</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3903,49 +4367,57 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>251800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>251700</v>
+      </c>
+      <c r="F96" s="3">
         <v>364100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>335100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>214800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>231400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>187000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>188300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>115500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>110600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>157800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>157000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>110600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>101500</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3985,8 +4457,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4026,8 +4504,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4067,127 +4551,151 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-123900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-123800</v>
+      </c>
+      <c r="F100" s="3">
         <v>590100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>543100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-723700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-779600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1078400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1085900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-399000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-382100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1235800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1229900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>415700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>381400</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>17300</v>
+      </c>
+      <c r="F101" s="3">
         <v>-33200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-33400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>7200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>6900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-46400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-46200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-19800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-18100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-54900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-58300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-796100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-795500</v>
+      </c>
+      <c r="F102" s="3">
         <v>488000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>449100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>67800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>73100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-754800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-760100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>557600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>534000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>288200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>286800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>233000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>213800</v>
       </c>
     </row>
